--- a/Garner_Statistical_Analysis.xlsx
+++ b/Garner_Statistical_Analysis.xlsx
@@ -513,13 +513,13 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -613,16 +613,16 @@
         <v>1</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>106.0974208923253</v>
+        <v>150.6472397039244</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1.490313943416333e-12</v>
+        <v>1.466903356497522e-16</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.08448095179358452</v>
+        <v>0.08904411473733931</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>1</v>
@@ -643,16 +643,16 @@
         <v>1</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>22.83757275904632</v>
+        <v>26.46229052255512</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2.642516989151899e-05</v>
+        <v>4.709890745241153e-06</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.01621374511757692</v>
+        <v>0.01712719864062674</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>1</v>
@@ -673,16 +673,16 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>37.35293825146263</v>
+        <v>48.01461227674594</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>4.000512520611599e-07</v>
+        <v>8.537744545469807e-09</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.0257198569694689</v>
+        <v>0.02437793279161631</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>1</v>
@@ -715,7 +715,7 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
@@ -832,31 +832,31 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>2176</v>
+        <v>2210</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>2795</v>
+        <v>2841</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1113</v>
+        <v>1091</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>10.3</v>
+        <v>12.274</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>1.671</v>
+        <v>1.753</v>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
@@ -883,19 +883,19 @@
       <c r="D3" s="2" t="inlineStr"/>
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="n">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>4.779</v>
+        <v>5.144</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>2.6e-05</v>
+        <v>5e-06</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.775</v>
+        <v>0.735</v>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
@@ -903,16 +903,16 @@
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>2355</v>
+        <v>2392</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>934</v>
+        <v>914</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>2616</v>
+        <v>2659</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="P3" s="2" t="inlineStr"/>
       <c r="Q3" s="2" t="inlineStr"/>
@@ -930,19 +930,19 @@
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="n">
-        <v>-1474</v>
+        <v>-1539</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>-7.055</v>
+        <v>-9.228</v>
       </c>
       <c r="I4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-2.321</v>
+        <v>-2.664</v>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
@@ -954,16 +954,16 @@
       <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="2" t="inlineStr"/>
       <c r="P4" s="2" t="n">
-        <v>1767</v>
+        <v>1756</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>611</v>
+        <v>550</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>3242</v>
+        <v>3295</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>660</v>
+        <v>604</v>
       </c>
     </row>
   </sheetData>
@@ -1063,31 +1063,31 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1526</v>
+        <v>1506</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>531</v>
+        <v>479</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>2008</v>
+        <v>2005</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>708</v>
+        <v>636</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>482</v>
+        <v>499</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>7.78</v>
+        <v>9.978</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>1.785</v>
+        <v>2.037</v>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
@@ -1107,31 +1107,31 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>2860</v>
+        <v>2914</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>524</v>
+        <v>482</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>3623</v>
+        <v>3676</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>825</v>
+        <v>762</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>762</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>7.979</v>
+        <v>9.218</v>
       </c>
       <c r="I3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>1.881</v>
+        <v>1.882</v>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
@@ -1241,31 +1241,31 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1635</v>
+        <v>1637</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>528</v>
+        <v>475</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1899</v>
+        <v>1875</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>703</v>
+        <v>635</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>264</v>
+        <v>239</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>4.885</v>
+        <v>5.254</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.000103</v>
+        <v>2.2e-05</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>1.121</v>
+        <v>1.072</v>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
@@ -1285,35 +1285,35 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>3112</v>
+        <v>3148</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>615</v>
+        <v>552</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>3371</v>
+        <v>3442</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>762</v>
+        <v>729</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>259</v>
+        <v>294</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>2.623</v>
+        <v>3.13</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.017246</v>
+        <v>0.004549</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.618</v>
+        <v>0.639</v>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>**</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -1437,10 +1437,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>482</v>
+        <v>499</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>270</v>
+        <v>245</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>762</v>
@@ -1449,23 +1449,23 @@
         <v>405</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-280</v>
+        <v>-263</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>-2.485</v>
+        <v>-2.722</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.017616</v>
+        <v>0.009013999999999999</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0.8169999999999999</v>
+        <v>-0.786</v>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>**</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr"/>
@@ -1484,19 +1484,19 @@
       <c r="D3" s="2" t="inlineStr"/>
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="n">
-        <v>6</v>
+        <v>-55</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.05</v>
+        <v>-0.528</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.960361</v>
+        <v>0.5996590000000001</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.016</v>
+        <v>-0.153</v>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
@@ -1504,16 +1504,16 @@
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>264</v>
+        <v>239</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>259</v>
+        <v>294</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>418</v>
+        <v>460</v>
       </c>
     </row>
   </sheetData>
@@ -1538,7 +1538,7 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="5" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
   </cols>
@@ -1607,31 +1607,31 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>2499</v>
+        <v>2548</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>977</v>
+        <v>966</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>3091</v>
+        <v>3133</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1311</v>
+        <v>1283</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>5.842</v>
+        <v>6.475</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1e-06</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.948</v>
+        <v>0.925</v>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
@@ -1710,13 +1710,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>2945</v>
+        <v>2967</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>609</v>
+        <v>537</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -1736,13 +1736,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>2776</v>
+        <v>2861</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -1762,13 +1762,13 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>3280</v>
+        <v>3329</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>706</v>
+        <v>660</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
@@ -1788,13 +1788,13 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>3966</v>
+        <v>4023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1117</v>
+        <v>1046</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
@@ -1814,13 +1814,13 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1514</v>
+        <v>1506</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>557</v>
+        <v>497</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
@@ -1840,13 +1840,13 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1538</v>
+        <v>1507</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>541</v>
+        <v>491</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8">
@@ -1866,13 +1866,13 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1756</v>
+        <v>1767</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>545</v>
+        <v>489</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9">
@@ -1892,13 +1892,13 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>2261</v>
+        <v>2244</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>925</v>
+        <v>829</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/Garner_Statistical_Analysis.xlsx
+++ b/Garner_Statistical_Analysis.xlsx
@@ -513,13 +513,13 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -556,7 +556,7 @@
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
     <col width="7" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
@@ -613,16 +613,16 @@
         <v>1</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>150.6472397039244</v>
+        <v>159.3166395670646</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1.466903356497522e-16</v>
+        <v>2.591242441114446e-17</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.08904411473733931</v>
+        <v>0.09418162492354219</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>1</v>
@@ -643,16 +643,16 @@
         <v>1</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>26.46229052255512</v>
+        <v>23.36700987762027</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4.709890745241153e-06</v>
+        <v>1.270189554393751e-05</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.01712719864062674</v>
+        <v>0.01517843980334036</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>1</v>
@@ -673,16 +673,16 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>48.01461227674594</v>
+        <v>46.08354540848087</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>8.537744545469807e-09</v>
+        <v>1.174892855964739e-08</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.02437793279161631</v>
+        <v>0.02284788884974949</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>1</v>
@@ -715,7 +715,7 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
@@ -832,31 +832,31 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>2210</v>
+        <v>2208</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>852</v>
+        <v>842</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>2841</v>
+        <v>2854</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1091</v>
+        <v>1084</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>631</v>
+        <v>646</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>12.274</v>
+        <v>12.622</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>1.753</v>
+        <v>1.767</v>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
@@ -883,19 +883,19 @@
       <c r="D3" s="2" t="inlineStr"/>
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="n">
-        <v>266</v>
+        <v>249</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>5.144</v>
+        <v>4.834</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>5e-06</v>
+        <v>1.3e-05</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.735</v>
+        <v>0.677</v>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
@@ -903,16 +903,16 @@
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>2392</v>
+        <v>2407</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>2659</v>
+        <v>2655</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>1040</v>
+        <v>1027</v>
       </c>
       <c r="P3" s="2" t="inlineStr"/>
       <c r="Q3" s="2" t="inlineStr"/>
@@ -930,19 +930,19 @@
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="n">
-        <v>-1539</v>
+        <v>-1533</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>-9.228</v>
+        <v>-9.550000000000001</v>
       </c>
       <c r="I4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-2.664</v>
+        <v>-2.701</v>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
@@ -954,16 +954,16 @@
       <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="2" t="inlineStr"/>
       <c r="P4" s="2" t="n">
-        <v>1756</v>
+        <v>1765</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>550</v>
+        <v>541</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>3295</v>
+        <v>3297</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>604</v>
+        <v>593</v>
       </c>
     </row>
   </sheetData>
@@ -987,7 +987,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
     <col width="5" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
@@ -1063,31 +1063,31 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1506</v>
+        <v>1511</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>2005</v>
+        <v>2018</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>636</v>
+        <v>627</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>9.978</v>
+        <v>10.398</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>2.037</v>
+        <v>2.08</v>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
@@ -1107,31 +1107,31 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>2914</v>
+        <v>2906</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>3676</v>
+        <v>3689</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>762</v>
+        <v>750</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>762</v>
+        <v>784</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>9.218</v>
+        <v>9.523</v>
       </c>
       <c r="I3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>1.882</v>
+        <v>1.905</v>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
@@ -1241,31 +1241,31 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1637</v>
+        <v>1651</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1875</v>
+        <v>1879</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>635</v>
+        <v>623</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>5.254</v>
+        <v>5.064</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>2.2e-05</v>
+        <v>3.2e-05</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>1.072</v>
+        <v>1.013</v>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
@@ -1285,31 +1285,31 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>3148</v>
+        <v>3163</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>3442</v>
+        <v>3432</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>729</v>
+        <v>717</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>294</v>
+        <v>269</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>3.13</v>
+        <v>2.883</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.004549</v>
+        <v>0.007988</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.639</v>
+        <v>0.577</v>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
@@ -1437,31 +1437,31 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>762</v>
+        <v>784</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-263</v>
+        <v>-276</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>-2.722</v>
+        <v>-2.883</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.009013999999999999</v>
+        <v>0.005796</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0.786</v>
+        <v>-0.8149999999999999</v>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
@@ -1484,19 +1484,19 @@
       <c r="D3" s="2" t="inlineStr"/>
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="n">
-        <v>-55</v>
+        <v>-42</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>-0.528</v>
+        <v>-0.401</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.5996590000000001</v>
+        <v>0.69033</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>-0.153</v>
+        <v>-0.113</v>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
@@ -1504,16 +1504,16 @@
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>294</v>
+        <v>269</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>460</v>
+        <v>467</v>
       </c>
     </row>
   </sheetData>
@@ -1607,31 +1607,31 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>2548</v>
+        <v>2576</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>966</v>
+        <v>975</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>3133</v>
+        <v>3131</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1283</v>
+        <v>1267</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>585</v>
+        <v>555</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>6.475</v>
+        <v>6.197</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.925</v>
+        <v>0.868</v>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
@@ -1710,13 +1710,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>2967</v>
+        <v>2963</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>537</v>
+        <v>527</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
@@ -1736,13 +1736,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>2861</v>
+        <v>2848</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
@@ -1762,13 +1762,13 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>3329</v>
+        <v>3363</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>660</v>
+        <v>669</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
@@ -1788,13 +1788,13 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>4023</v>
+        <v>4016</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1046</v>
+        <v>1026</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
@@ -1814,13 +1814,13 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1506</v>
+        <v>1511</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>497</v>
+        <v>488</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
@@ -1840,13 +1840,13 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1507</v>
+        <v>1510</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>491</v>
+        <v>482</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8">
@@ -1866,13 +1866,13 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1767</v>
+        <v>1790</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9">
@@ -1892,13 +1892,13 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>2244</v>
+        <v>2247</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>829</v>
+        <v>812</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
